--- a/images/document/Tổng hợp biểu mẫu nhập liệu thủ công.xlsx
+++ b/images/document/Tổng hợp biểu mẫu nhập liệu thủ công.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10909"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10927"/>
   <workbookPr updateLinks="always"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/d39b8747432be571/Work/04. Company/Synodus/GOV/01.VNA/VNA/images/document/OneDrive_1_9-17-2026/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/d39b8747432be571/Work/04. Company/Synodus/GOV/01.VNA/VNA/images/document/"/>
     </mc:Choice>
   </mc:AlternateContent>
   <xr:revisionPtr revIDLastSave="399" documentId="13_ncr:1_{42B34BF5-E2CD-48B5-A15B-9BDA1D6D15FD}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{79A2F494-1077-4C10-9821-EAEF5AE310AC}"/>
   <bookViews>
-    <workbookView xWindow="14300" yWindow="500" windowWidth="19400" windowHeight="10280" firstSheet="1" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="14200" yWindow="500" windowWidth="19400" windowHeight="10280" firstSheet="1" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Tổng quan" sheetId="23" r:id="rId1"/>
@@ -3443,6 +3443,15 @@
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
+<?mso-contentType ?>
+<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
+  <Display>DocumentLibraryForm</Display>
+  <Edit>DocumentLibraryForm</Edit>
+  <New>DocumentLibraryForm</New>
+</FormTemplates>
+</file>
+
+<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
 <ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="Document" ma:contentTypeID="0x010100A638FA6C959AA742BBD124ED0D0C8AD5" ma:contentTypeVersion="11" ma:contentTypeDescription="Create a new document." ma:contentTypeScope="" ma:versionID="618351c9ea45c13f4c7623819a05fa0c">
   <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns2="6d24557e-9262-4bcf-8dfb-0861ee36c1b8" xmlns:ns3="ce7e1783-cf63-422b-b1eb-d7674af17c37" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="aec01ad65f4c905f4e6f5ceba3b7c2e0" ns2:_="" ns3:_="">
     <xsd:import namespace="6d24557e-9262-4bcf-8dfb-0861ee36c1b8"/>
@@ -3637,15 +3646,6 @@
 </ct:contentTypeSchema>
 </file>
 
-<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
-<?mso-contentType ?>
-<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
-  <Display>DocumentLibraryForm</Display>
-  <Edit>DocumentLibraryForm</Edit>
-  <New>DocumentLibraryForm</New>
-</FormTemplates>
-</file>
-
 <file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
 <p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
   <documentManagement>
@@ -3658,6 +3658,14 @@
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{8AE3A085-DB4D-4EF4-B7E6-268E6F720FB4}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
+</file>
+
+<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{9B320C32-DADE-4C78-A8FE-B54DF9A8660E}">
   <ds:schemaRefs>
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/contentType"/>
@@ -3676,14 +3684,6 @@
 </ds:datastoreItem>
 </file>
 
-<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{8AE3A085-DB4D-4EF4-B7E6-268E6F720FB4}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
-</file>
-
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{2617E608-3F84-4D3F-B679-9D36A1ECF24B}">
   <ds:schemaRefs>
